--- a/Source Data/Source Data Fig. 2.xlsx
+++ b/Source Data/Source Data Fig. 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/e1135497_u_nus_edu/Documents/Lab Document/Projects/Fiber display/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{BD068AF0-6741-4348-8AE4-F20033F48ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2890ADB3-7762-4D6C-A248-7CD35DB6B13D}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{BD068AF0-6741-4348-8AE4-F20033F48ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC9C34C7-B61E-49F7-8914-4E15294D00FD}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="5550" windowWidth="23370" windowHeight="11715" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7140" yWindow="5550" windowWidth="23370" windowHeight="11715" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 2d" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Fibre Length (m)</t>
   </si>
@@ -194,6 +194,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9286,7 +9290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08208D88-6288-4666-A81D-DE421844F72A}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -9295,7 +9299,7 @@
     <col min="4" max="4" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -9314,8 +9318,23 @@
       <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>0</v>
       </c>
@@ -9334,8 +9353,23 @@
       <c r="F2">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>1008</v>
+      </c>
+      <c r="H2">
+        <v>1008</v>
+      </c>
+      <c r="I2">
+        <v>998</v>
+      </c>
+      <c r="J2">
+        <v>1004.67</v>
+      </c>
+      <c r="K2">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>200</v>
       </c>
@@ -9354,8 +9388,23 @@
       <c r="F3">
         <v>0.46</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>1019</v>
+      </c>
+      <c r="H3">
+        <v>1007</v>
+      </c>
+      <c r="I3">
+        <v>1008</v>
+      </c>
+      <c r="J3">
+        <v>1011.33</v>
+      </c>
+      <c r="K3">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>400</v>
       </c>
@@ -9374,8 +9423,23 @@
       <c r="F4">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>1012</v>
+      </c>
+      <c r="H4">
+        <v>1014</v>
+      </c>
+      <c r="I4">
+        <v>1019</v>
+      </c>
+      <c r="J4">
+        <v>1015</v>
+      </c>
+      <c r="K4">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>600</v>
       </c>
@@ -9394,8 +9458,23 @@
       <c r="F5">
         <v>0.63</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>1020</v>
+      </c>
+      <c r="H5">
+        <v>1030</v>
+      </c>
+      <c r="I5">
+        <v>1031</v>
+      </c>
+      <c r="J5">
+        <v>1027</v>
+      </c>
+      <c r="K5">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>800</v>
       </c>
@@ -9414,8 +9493,23 @@
       <c r="F6">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>1023</v>
+      </c>
+      <c r="H6">
+        <v>1024</v>
+      </c>
+      <c r="I6">
+        <v>1028</v>
+      </c>
+      <c r="J6">
+        <v>1025</v>
+      </c>
+      <c r="K6">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>1000</v>
       </c>
@@ -9434,144 +9528,19 @@
       <c r="F7">
         <v>0.44</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10">
-        <v>1008</v>
-      </c>
-      <c r="C10">
-        <v>1008</v>
-      </c>
-      <c r="D10">
-        <v>998</v>
-      </c>
-      <c r="E10">
-        <v>1004.67</v>
-      </c>
-      <c r="F10">
-        <v>5.77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>200</v>
-      </c>
-      <c r="B11">
-        <v>1019</v>
-      </c>
-      <c r="C11">
-        <v>1007</v>
-      </c>
-      <c r="D11">
-        <v>1008</v>
-      </c>
-      <c r="E11">
-        <v>1011.33</v>
-      </c>
-      <c r="F11">
-        <v>6.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>400</v>
-      </c>
-      <c r="B12">
-        <v>1012</v>
-      </c>
-      <c r="C12">
-        <v>1014</v>
-      </c>
-      <c r="D12">
-        <v>1019</v>
-      </c>
-      <c r="E12">
-        <v>1015</v>
-      </c>
-      <c r="F12">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>600</v>
-      </c>
-      <c r="B13">
-        <v>1020</v>
-      </c>
-      <c r="C13">
-        <v>1030</v>
-      </c>
-      <c r="D13">
-        <v>1031</v>
-      </c>
-      <c r="E13">
+      <c r="G7">
         <v>1027</v>
       </c>
-      <c r="F13">
-        <v>6.08</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>800</v>
-      </c>
-      <c r="B14">
-        <v>1023</v>
-      </c>
-      <c r="C14">
-        <v>1024</v>
-      </c>
-      <c r="D14">
-        <v>1028</v>
-      </c>
-      <c r="E14">
-        <v>1025</v>
-      </c>
-      <c r="F14">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>1000</v>
-      </c>
-      <c r="B15">
-        <v>1027</v>
-      </c>
-      <c r="C15">
+      <c r="H7">
         <v>1029</v>
       </c>
-      <c r="D15">
+      <c r="I7">
         <v>1036</v>
       </c>
-      <c r="E15">
+      <c r="J7">
         <v>1030.67</v>
       </c>
-      <c r="F15">
+      <c r="K7">
         <v>4.7300000000000004</v>
       </c>
     </row>

--- a/Source Data/Source Data Fig. 2.xlsx
+++ b/Source Data/Source Data Fig. 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nusu-my.sharepoint.com/personal/e1135497_u_nus_edu/Documents/Lab Document/Projects/Fiber display/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{BD068AF0-6741-4348-8AE4-F20033F48ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC9C34C7-B61E-49F7-8914-4E15294D00FD}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{BD068AF0-6741-4348-8AE4-F20033F48ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527ED56C-4588-48DF-915C-922547EF0B7C}"/>
   <bookViews>
-    <workbookView xWindow="7140" yWindow="5550" windowWidth="23370" windowHeight="11715" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7140" yWindow="5550" windowWidth="23370" windowHeight="11715" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 2d" sheetId="1" r:id="rId1"/>
@@ -57,22 +57,6 @@
     <t>Illuminance 1 (lux)</t>
   </si>
   <si>
-    <t>Pressure (kPa)</t>
-  </si>
-  <si>
-    <t>Pressing cycles</t>
-  </si>
-  <si>
-    <t>Position  (mm)</t>
-  </si>
-  <si>
-    <t>Resistance 1 (kΩ)</t>
-  </si>
-  <si>
-    <t>Conductance (μS)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Illuminance 2 (lux)</t>
   </si>
   <si>
@@ -85,6 +69,9 @@
     <t>SD (lux)</t>
   </si>
   <si>
+    <t>Resistance 1 (kΩ)</t>
+  </si>
+  <si>
     <t>Resistance 2 (kΩ)</t>
   </si>
   <si>
@@ -95,6 +82,19 @@
   </si>
   <si>
     <t>SD (kΩ)</t>
+  </si>
+  <si>
+    <t>Pressure (kPa)</t>
+  </si>
+  <si>
+    <t>Conductance (μS)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pressing cycles</t>
+  </si>
+  <si>
+    <t>Position  (mm)</t>
   </si>
   <si>
     <t>test1 (ADC reading)</t>
@@ -126,7 +126,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -178,10 +178,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -194,10 +194,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9307,31 +9303,31 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -9561,10 +9557,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -9601,7 +9597,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>165</v>
+        <v>164.44</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -9696,10 +9692,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -17724,7 +17720,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>18</v>
